--- a/resampling/input/accessibility_reports_generated/MDM_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/MDM_accessibility_report.xlsx
@@ -184,8 +184,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q13" headerRowCount="1">
-  <autoFilter ref="A1:Q13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q20" headerRowCount="1">
+  <autoFilter ref="A1:Q20"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -553,7 +553,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 12 wards, 17 clusters</t>
+          <t>Assigned to you: 19 wards, 17 clusters</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -833,25 +833,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sandamu</t>
+          <t>Fago B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -874,33 +882,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fago B</t>
+          <t>Fago A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Zango</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -923,7 +923,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rade A</t>
+          <t>Sandamu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -935,13 +935,13 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -964,25 +964,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rade B</t>
+          <t>Katsayal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1005,7 +1013,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fago A</t>
+          <t>Rade A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1017,13 +1025,13 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1046,7 +1054,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Karkarku</t>
+          <t>Daneji B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1058,13 +1066,13 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1087,7 +1095,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Katsayal</t>
+          <t>Rade B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1099,13 +1107,13 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1128,25 +1136,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Daneji B</t>
+          <t>Kagare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1175,11 +1191,19 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Daura</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1187,7 +1211,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1210,7 +1234,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kagare</t>
+          <t>Achilafiya</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1222,13 +1246,13 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1251,25 +1275,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kwasarawa</t>
+          <t>Dan Aunai</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dutsi</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1292,7 +1324,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Madobi B</t>
+          <t>Dargage</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1303,7 +1335,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Daura</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1312,7 +1344,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1328,23 +1360,358 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Garni</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Baure; Zango</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" s="10" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Karkarku</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Daura; Mai'adua</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" s="10" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Kwasarawa</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mai'adua; Zango</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" s="10" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Madobi B</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Daura</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" s="10" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ruwan Kaya A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Daura; Dutsi</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" s="10" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sabon Gari</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bindawa; Charanchi; Daura; Funtua; Mai'adua; Mani; Rimi</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" s="10" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Yola</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" s="10" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="K2:K13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="O2:O20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1568,7 +1935,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rade A</t>
+          <t>Daneji A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1883,7 +2250,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Daneji A</t>
+          <t>Rade A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1928,7 +2295,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rade B</t>
+          <t>Daneji B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2153,7 +2520,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fago B</t>
+          <t>Rade B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2246,7 +2613,7 @@
     </dataValidation>
     <dataValidation sqref="M2:M18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2512,13 +2879,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40B522E0-BCA1-4965-94CC-190D2419164E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EFB2941-4C37-44AD-94A1-E055E10DC9F7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2657D65-F112-4DBC-A1CA-81211385BEC7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE69862B-CF6F-4505-8C31-8C4B5D4FE3BA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A581135-AB9D-42C3-8CCE-FC6A39983A88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4912CE16-60CE-4419-9A23-3857C1BDA434}"/>
 </file>
--- a/resampling/input/accessibility_reports_generated/MDM_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/MDM_accessibility_report.xlsx
@@ -210,24 +210,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O18" headerRowCount="1">
-  <autoFilter ref="A1:O18"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:P28" headerRowCount="1">
+  <autoFilter ref="A1:P28"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
     <tableColumn id="3" name="Ward (GRID3)"/>
     <tableColumn id="4" name="Pop Type"/>
     <tableColumn id="5" name="Cluster ID"/>
-    <tableColumn id="6" name="IDP Category"/>
-    <tableColumn id="7" name="Target HHs (primary)"/>
-    <tableColumn id="8" name="Reserve HHs"/>
-    <tableColumn id="9" name="Accessible (Y/N)"/>
-    <tableColumn id="10" name="Reason category"/>
-    <tableColumn id="11" name="Reason notes"/>
-    <tableColumn id="12" name="% of target achieved so far"/>
-    <tableColumn id="13" name="Date reported"/>
-    <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
-    <tableColumn id="15" name="Source channel"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="IDP Category"/>
+    <tableColumn id="8" name="Target HHs (primary)"/>
+    <tableColumn id="9" name="Reserve HHs"/>
+    <tableColumn id="10" name="Accessible (Y/N)"/>
+    <tableColumn id="11" name="Reason category"/>
+    <tableColumn id="12" name="Reason notes"/>
+    <tableColumn id="13" name="% of target achieved so far"/>
+    <tableColumn id="14" name="Date reported"/>
+    <tableColumn id="15" name="Reported by (Partner / IMPACT-default)"/>
+    <tableColumn id="16" name="Source channel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -522,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -553,7 +554,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 19 wards, 17 clusters</t>
+          <t>Assigned to you: 19 wards, 27 clusters</t>
         </is>
       </c>
     </row>
@@ -580,7 +581,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
+          <t>If you've reported on a row before, your last answer is already shown here (Accessible/Reason/Date reported etc.) rather than a blank cell - please review it and only change it if something has actually changed since you last told us, don't assume a filled-in row is a mistake. On the 'Cluster Accessibility' sheet, a cluster you previously flagged that's since been removed from your assigned list entirely still appears, marked 'No longer in frame' in the Status column - kept so your earlier report isn't lost, but it's no longer something we need action on.</t>
         </is>
       </c>
     </row>
@@ -590,7 +591,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
+          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
         </is>
       </c>
     </row>
@@ -600,7 +601,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
+          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
         </is>
       </c>
     </row>
@@ -610,7 +611,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
+          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
         </is>
       </c>
     </row>
@@ -620,7 +621,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
+          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
         </is>
       </c>
     </row>
@@ -630,7 +631,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
         </is>
       </c>
     </row>
@@ -640,58 +641,68 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>IMPORTANT: please review your ENTIRE coverage area in one pass before sending this back to us, rather than reporting a few wards now and more later - this significantly cuts down the back-and-forth rounds we need with you. If genuinely new information comes in afterwards, send an updated copy of the FULL sheet (not just the changed rows) with a new Date reported - we track changes over time by date, so we don't need you to tell us what changed, just the current full picture.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Use for</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Ward Accessibility</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>Ward Accessibility</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -833,33 +844,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fago B</t>
+          <t>Sandamu</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Zango</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -882,25 +885,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fago A</t>
+          <t>Fago B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -923,7 +934,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sandamu</t>
+          <t>Fago A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -935,13 +946,13 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -1711,7 +1722,7 @@
     </dataValidation>
     <dataValidation sqref="O2:O20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1727,7 +1738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1735,16 +1746,17 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1775,50 +1787,55 @@
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
           <t>IDP Category</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Target HHs (primary)</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Reserve HHs</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Accessible (Y/N)</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Reason category</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Reason notes</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>% of target achieved so far</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Date reported</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Reported by (Partner / IMPACT-default)</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Source channel</t>
         </is>
@@ -1852,26 +1869,31 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1901,26 +1923,31 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1935,23 +1962,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Daneji A</t>
+          <t>Sandamu</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>idp_NG021033_supp1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1959,13 +1990,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1980,23 +2016,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fago B</t>
+          <t>Sandamu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_10</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>idp_NG021033_supp10</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2004,13 +2044,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2025,23 +2070,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fago A</t>
+          <t>Sandamu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_11</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>idp_NG021033_supp2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2049,13 +2098,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2070,23 +2124,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kagare</t>
+          <t>Sandamu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_12</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>idp_NG021033_supp3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2094,13 +2152,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2115,37 +2178,46 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Katsayal</t>
+          <t>Sandamu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_13</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>idp_NG021033_supp4</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2160,23 +2232,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fago B</t>
+          <t>Sandamu</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_15</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>idp_NG021033_supp5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2184,13 +2260,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2205,23 +2286,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Daneji B</t>
+          <t>Sandamu</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_16</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>idp_NG021033_supp6</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2229,13 +2314,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2250,23 +2340,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rade A</t>
+          <t>Sandamu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_17</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>idp_NG021033_supp7</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2274,13 +2368,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2295,23 +2394,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Daneji B</t>
+          <t>Sandamu</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_2</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>idp_NG021033_supp8</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2319,13 +2422,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2345,18 +2453,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_3</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>idp_NG021033_supp9</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2364,13 +2476,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2385,7 +2502,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rade B</t>
+          <t>Daneji A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2395,27 +2512,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_4</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021033_1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2430,7 +2552,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rade A</t>
+          <t>Fago B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2440,27 +2562,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_5</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>non_idp_NG021033_10</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2475,7 +2602,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sandamu</t>
+          <t>Fago A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2485,27 +2612,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_7</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021033_11</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2520,7 +2652,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rade B</t>
+          <t>Kagare</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2530,27 +2662,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_8</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021033_12</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2565,7 +2702,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sandamu</t>
+          <t>Katsayal</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2575,45 +2712,550 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>non_idp_NG021033_9</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021033_13</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fago B</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>non_idp_NG021033_15</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Daneji B</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>non_idp_NG021033_16</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rade A</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>non_idp_NG021033_17</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Daneji B</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>non_idp_NG021033_2</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>non_idp_NG021033_3</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Rade B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>non_idp_NG021033_4</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Rade A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>non_idp_NG021033_5</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>non_idp_NG021033_7</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Rade B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>non_idp_NG021033_8</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>non_idp_NG021033_9</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="N2:N28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2879,13 +3521,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EFB2941-4C37-44AD-94A1-E055E10DC9F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8541855F-D095-4891-993A-0FA8671BB9F6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE69862B-CF6F-4505-8C31-8C4B5D4FE3BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F221C74-B59F-4D98-A662-59CEAEFD9B97}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4912CE16-60CE-4419-9A23-3857C1BDA434}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{845D8937-AAFB-4A69-B96A-E7A447EAF936}"/>
 </file>